--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.95567812904052</v>
+        <v>4.867797695969085</v>
       </c>
       <c r="D2" t="n">
-        <v>29.69403770146368</v>
+        <v>4.825281126487848</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F2" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.31833789255361</v>
+        <v>3.951729907539963</v>
       </c>
       <c r="D3" t="n">
-        <v>18.1578323556899</v>
+        <v>2.950647757799608</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F3" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.2488495233458</v>
+        <v>6.540438047543693</v>
       </c>
       <c r="D4" t="n">
-        <v>37.45840343512493</v>
+        <v>6.086990558207801</v>
       </c>
       <c r="E4" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F4" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.72446662952339</v>
+        <v>5.805225827297551</v>
       </c>
       <c r="D5" t="n">
-        <v>25.60772243781108</v>
+        <v>4.161254896144301</v>
       </c>
       <c r="E5" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F5" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.70885296096382</v>
+        <v>3.690188606156621</v>
       </c>
       <c r="D6" t="n">
-        <v>22.69739511862834</v>
+        <v>3.688326706777105</v>
       </c>
       <c r="E6" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F6" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.42068376448618</v>
+        <v>4.293361111729005</v>
       </c>
       <c r="D7" t="n">
-        <v>22.87364483878615</v>
+        <v>3.716967286302749</v>
       </c>
       <c r="E7" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F7" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.75213077499526</v>
+        <v>4.99722125093673</v>
       </c>
       <c r="D8" t="n">
-        <v>30.89191584913796</v>
+        <v>5.019936325484919</v>
       </c>
       <c r="E8" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F8" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.84173818550242</v>
+        <v>6.636782455144144</v>
       </c>
       <c r="D9" t="n">
-        <v>40.19817757479463</v>
+        <v>6.532203855904128</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F9" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.66835560571516</v>
+        <v>4.983607785928713</v>
       </c>
       <c r="D10" t="n">
-        <v>23.99080506588285</v>
+        <v>3.898505823205964</v>
       </c>
       <c r="E10" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F10" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.197835273597</v>
+        <v>6.369648231959513</v>
       </c>
       <c r="D11" t="n">
-        <v>38.35582567022738</v>
+        <v>6.23282167141195</v>
       </c>
       <c r="E11" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F11" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.80239196914647</v>
+        <v>5.817888694986301</v>
       </c>
       <c r="D12" t="n">
-        <v>35.83449721647256</v>
+        <v>5.823105797676792</v>
       </c>
       <c r="E12" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F12" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.23795109640366</v>
+        <v>4.751167053165594</v>
       </c>
       <c r="D13" t="n">
-        <v>28.18903881548917</v>
+        <v>4.580718807516991</v>
       </c>
       <c r="E13" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F13" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.96771149539223</v>
+        <v>3.244753118001237</v>
       </c>
       <c r="D14" t="n">
-        <v>19.36920083324734</v>
+        <v>3.147495135402692</v>
       </c>
       <c r="E14" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F14" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.43600344514535</v>
+        <v>5.433350559836119</v>
       </c>
       <c r="D15" t="n">
-        <v>33.49178533387602</v>
+        <v>5.442415116754854</v>
       </c>
       <c r="E15" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F15" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.65402352314287</v>
+        <v>4.818778822510716</v>
       </c>
       <c r="D16" t="n">
-        <v>37.58175683364661</v>
+        <v>6.107035485467574</v>
       </c>
       <c r="E16" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F16" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.70555914596448</v>
+        <v>4.827153361219229</v>
       </c>
       <c r="D17" t="n">
-        <v>31.75330447202434</v>
+        <v>5.159911976703955</v>
       </c>
       <c r="E17" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F17" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.36058580522722</v>
+        <v>2.983595193349423</v>
       </c>
       <c r="D18" t="n">
-        <v>18.76692528417524</v>
+        <v>3.049625358678477</v>
       </c>
       <c r="E18" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F18" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.88187638289137</v>
+        <v>3.555804912219848</v>
       </c>
       <c r="D19" t="n">
-        <v>21.78637535474256</v>
+        <v>3.540285995145666</v>
       </c>
       <c r="E19" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F19" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>17.02041258149885</v>
+        <v>2.765817044493564</v>
       </c>
       <c r="D20" t="n">
-        <v>3.846004019355422</v>
+        <v>0.624975653145256</v>
       </c>
       <c r="E20" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F20" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>15.37641636733062</v>
+        <v>2.498667659691226</v>
       </c>
       <c r="D21" t="n">
-        <v>15.29115457951685</v>
+        <v>2.484812619171488</v>
       </c>
       <c r="E21" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F21" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>19.49610490152711</v>
+        <v>3.168117046498155</v>
       </c>
       <c r="D22" t="n">
-        <v>19.34607790094896</v>
+        <v>3.143737658904206</v>
       </c>
       <c r="E22" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F22" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>19.11674448107304</v>
+        <v>3.106470978174369</v>
       </c>
       <c r="D23" t="n">
-        <v>19.15384542626989</v>
+        <v>3.112499881768857</v>
       </c>
       <c r="E23" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F23" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>13.45047332667015</v>
+        <v>2.1857019155839</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2841294490578</v>
+        <v>2.158671035471892</v>
       </c>
       <c r="E24" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F24" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>19.98973305029275</v>
+        <v>3.248331620672571</v>
       </c>
       <c r="D25" t="n">
-        <v>20.16555202822251</v>
+        <v>3.276902204586158</v>
       </c>
       <c r="E25" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F25" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>40.19244329831303</v>
+        <v>6.531272035975868</v>
       </c>
       <c r="D26" t="n">
-        <v>34.13909107264903</v>
+        <v>5.547602299305468</v>
       </c>
       <c r="E26" t="n">
-        <v>8.2457906408446</v>
+        <v>1.339940979137248</v>
       </c>
       <c r="F26" t="n">
-        <v>8.954116535079185</v>
+        <v>1.455043936950367</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
